--- a/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/ManualSettle001.xlsx
+++ b/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/ManualSettle001.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11865" windowHeight="6645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="11870" windowHeight="6650"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>交收状态</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -41,10 +41,6 @@
   </si>
   <si>
     <t>交易市场</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>交易平台</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -467,31 +463,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:Y1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="11.75" customWidth="1"/>
-    <col min="7" max="7" width="11.75" customWidth="1"/>
-    <col min="18" max="18" width="13.75" customWidth="1"/>
-    <col min="19" max="19" width="11.875" customWidth="1"/>
-    <col min="20" max="20" width="10.25" customWidth="1"/>
-    <col min="22" max="22" width="11.75" customWidth="1"/>
-    <col min="24" max="24" width="9.75" customWidth="1"/>
+    <col min="1" max="1" width="5.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="11.7265625" customWidth="1"/>
+    <col min="7" max="7" width="11.7265625" customWidth="1"/>
+    <col min="17" max="17" width="13.7265625" customWidth="1"/>
+    <col min="18" max="18" width="11.90625" customWidth="1"/>
+    <col min="19" max="19" width="10.26953125" customWidth="1"/>
+    <col min="21" max="21" width="11.7265625" customWidth="1"/>
+    <col min="23" max="23" width="9.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
@@ -515,7 +511,7 @@
         <v>6</v>
       </c>
       <c r="L1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M1" t="s">
         <v>10</v>
@@ -555,9 +551,6 @@
       </c>
       <c r="Y1" t="s">
         <v>22</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
